--- a/reconcile/storage/output/ongoing/ongoing_battery_by_iso2_inst_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_battery_by_iso2_inst_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU21"/>
+  <dimension ref="A1:BV21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,220 +582,225 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>DE | ford</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>IT | sunlight group</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>LV | sia “ecolead”</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>GB | aesc</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>DE | fenecon</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>FR | automotive cell company</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>DE | bmw</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>DE | gotion high tech</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>DE | porsche</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>GR | sunlight group</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>NO | vianode</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>FR | verkor</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>HU | bmw</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>NO | freyr</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>DE | fenecon</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>FR | automotive cell company</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>DE | bmw</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>DE | gotion high tech</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>DE | porsche</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>GR | sunlight group</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>NO | vianode</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>FR | verkor</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>HU | bmw</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>NO | morrow batteries</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ES | volkswagen</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>HU | ecopro</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>PT | stellantis</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>RO | prime batteries technology</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>PL | lyten</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ES | seat</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>DE | lion smart</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>FI | finnish minerals beijing easpring</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>HU | eve energy</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>FR | aesc</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>GB | agratas</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ES | hyundai mobis</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>RO | draexlmaier group</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>DE | fraunhofer ffb</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ES | acciona</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ES | aesc</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>GB | atlantic green</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>PL | bmz poland</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>DE | man</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>SK | gotion inobat batteries</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>SE | volvo</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>FI | easpring finland new materials oy</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>GB | volklec</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>FI | finnish minerals group and beijing easpring material technology</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>FR | tiamat</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>HU | catl</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>BG | international power supply</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>DE | norcsi</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>DE | siemens</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>FI | finnish minerals group and beijing easpring</t>
         </is>
@@ -806,7 +811,7 @@
         <v>44286</v>
       </c>
       <c r="B2" t="n">
-        <v>337868.2764212993</v>
+        <v>337868.25</v>
       </c>
       <c r="C2" t="n">
         <v>16250000</v>
@@ -839,10 +844,10 @@
         <v>15000000</v>
       </c>
       <c r="M2" t="n">
-        <v>54957900.39412397</v>
+        <v>54957900.375</v>
       </c>
       <c r="N2" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="O2" t="n">
         <v>3500000</v>
@@ -872,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>147392290.2494331</v>
+        <v>147392290</v>
       </c>
       <c r="Y2" t="n">
         <v>1666666.666666667</v>
@@ -1019,6 +1024,9 @@
         <v>0</v>
       </c>
       <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1063,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="O3" t="n">
         <v>3500000</v>
@@ -1099,7 +1107,7 @@
         <v>5000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>474756179.1555439</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AA3" t="n">
         <v>416666.6666666667</v>
@@ -1111,7 +1119,7 @@
         <v>416666.6666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15580692.41666667</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -1240,6 +1248,9 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1284,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="O4" t="n">
         <v>3500000</v>
@@ -1320,7 +1331,7 @@
         <v>5000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>474756179.1555439</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AA4" t="n">
         <v>625000</v>
@@ -1332,14 +1343,14 @@
         <v>625000</v>
       </c>
       <c r="AD4" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2083333.333333333</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>181666.6666666667</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
@@ -1461,6 +1472,9 @@
         <v>0</v>
       </c>
       <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1505,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="O5" t="n">
         <v>3500000</v>
@@ -1526,7 +1540,7 @@
         <v>10000000</v>
       </c>
       <c r="U5" t="n">
-        <v>381948773.2095491</v>
+        <v>381948773.1923077</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1541,7 +1555,7 @@
         <v>5000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>474756179.1555439</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AA5" t="n">
         <v>625000</v>
@@ -1553,16 +1567,16 @@
         <v>625000</v>
       </c>
       <c r="AD5" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE5" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>545000</v>
       </c>
-      <c r="AF5" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1682,6 +1696,9 @@
         <v>0</v>
       </c>
       <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1726,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>96511354.5670491</v>
+        <v>96511354.56521739</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1747,7 +1764,7 @@
         <v>10000000</v>
       </c>
       <c r="U6" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1762,7 +1779,7 @@
         <v>5000000</v>
       </c>
       <c r="Z6" t="n">
-        <v>474756179.1555439</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AA6" t="n">
         <v>625000</v>
@@ -1774,16 +1791,16 @@
         <v>625000</v>
       </c>
       <c r="AD6" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE6" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>545000</v>
       </c>
-      <c r="AF6" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1903,6 +1920,9 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1947,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1968,7 +1988,7 @@
         <v>10000000</v>
       </c>
       <c r="U7" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1983,7 +2003,7 @@
         <v>5000000</v>
       </c>
       <c r="Z7" t="n">
-        <v>474756179.1555439</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AA7" t="n">
         <v>625000</v>
@@ -1995,16 +2015,16 @@
         <v>625000</v>
       </c>
       <c r="AD7" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE7" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>545000</v>
       </c>
-      <c r="AF7" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH7" t="n">
         <v>7500000</v>
@@ -2124,6 +2144,9 @@
         <v>0</v>
       </c>
       <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2168,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2189,7 +2212,7 @@
         <v>10000000</v>
       </c>
       <c r="U8" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2204,7 +2227,7 @@
         <v>5000000</v>
       </c>
       <c r="Z8" t="n">
-        <v>316504119.4370292</v>
+        <v>316504119.4117647</v>
       </c>
       <c r="AA8" t="n">
         <v>625000</v>
@@ -2216,16 +2239,16 @@
         <v>625000</v>
       </c>
       <c r="AD8" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE8" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>545000</v>
       </c>
-      <c r="AF8" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH8" t="n">
         <v>7500000</v>
@@ -2345,6 +2368,9 @@
         <v>0</v>
       </c>
       <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2389,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2410,7 +2436,7 @@
         <v>10000000</v>
       </c>
       <c r="U9" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2437,16 +2463,16 @@
         <v>625000</v>
       </c>
       <c r="AD9" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE9" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>545000</v>
       </c>
-      <c r="AF9" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH9" t="n">
         <v>7500000</v>
@@ -2473,14 +2499,14 @@
         <v>12500000</v>
       </c>
       <c r="AP9" t="n">
-        <v>117647058.8235294</v>
+        <v>23529411.76470588</v>
       </c>
       <c r="AQ9" t="n">
+        <v>147988649.2380952</v>
+      </c>
+      <c r="AR9" t="n">
         <v>40666666.66666666</v>
       </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
@@ -2566,6 +2592,9 @@
         <v>0</v>
       </c>
       <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2610,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2631,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2658,16 +2687,16 @@
         <v>625000</v>
       </c>
       <c r="AD10" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="AE10" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>545000</v>
       </c>
-      <c r="AF10" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH10" t="n">
         <v>7500000</v>
@@ -2694,17 +2723,17 @@
         <v>18750000</v>
       </c>
       <c r="AP10" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ10" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR10" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>145833333.3333333</v>
       </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
@@ -2787,6 +2816,9 @@
         <v>0</v>
       </c>
       <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2831,7 +2863,7 @@
         <v>28750000</v>
       </c>
       <c r="N11" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2852,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2879,16 +2911,16 @@
         <v>208333.3333333333</v>
       </c>
       <c r="AD11" t="n">
+        <v>31161384.83333333</v>
+      </c>
+      <c r="AE11" t="n">
         <v>6250000</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>545000</v>
       </c>
-      <c r="AF11" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH11" t="n">
         <v>7500000</v>
@@ -2915,29 +2947,29 @@
         <v>58750000</v>
       </c>
       <c r="AP11" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ11" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR11" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>19166666.66666667</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>10000000</v>
       </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
@@ -3008,6 +3040,9 @@
         <v>0</v>
       </c>
       <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,7 +3087,7 @@
         <v>43125000</v>
       </c>
       <c r="N12" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -3073,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -3100,16 +3135,16 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
         <v>4166666.666666667</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>363333.3333333333</v>
       </c>
-      <c r="AF12" t="n">
-        <v>82376311.2829254</v>
-      </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>85866766.375</v>
       </c>
       <c r="AH12" t="n">
         <v>7500000</v>
@@ -3136,38 +3171,38 @@
         <v>138750000</v>
       </c>
       <c r="AP12" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ12" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR12" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
       <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>64500000</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
       <c r="BA12" t="n">
         <v>0</v>
       </c>
@@ -3229,6 +3264,9 @@
         <v>0</v>
       </c>
       <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3273,7 +3311,7 @@
         <v>43125000</v>
       </c>
       <c r="N13" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -3357,44 +3395,44 @@
         <v>138750000</v>
       </c>
       <c r="AP13" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ13" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR13" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
       <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA13" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB13" t="n">
         <v>136842105.2631579</v>
       </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
@@ -3450,6 +3488,9 @@
         <v>0</v>
       </c>
       <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3494,7 +3535,7 @@
         <v>43125000</v>
       </c>
       <c r="N14" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3578,46 +3619,46 @@
         <v>138750000</v>
       </c>
       <c r="AP14" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ14" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR14" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
       <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA14" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB14" t="n">
         <v>205263157.8947369</v>
       </c>
-      <c r="BB14" t="n">
-        <v>388138487.8124514</v>
-      </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>388138487.8333333</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -3671,6 +3712,9 @@
         <v>0</v>
       </c>
       <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3715,7 +3759,7 @@
         <v>43125000</v>
       </c>
       <c r="N15" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3799,53 +3843,53 @@
         <v>138750000</v>
       </c>
       <c r="AP15" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ15" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AR15" t="n">
         <v>61000000</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
       <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA15" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB15" t="n">
         <v>205263157.8947369</v>
       </c>
-      <c r="BB15" t="n">
-        <v>582207731.7186772</v>
-      </c>
       <c r="BC15" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD15" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
@@ -3892,6 +3936,9 @@
         <v>0</v>
       </c>
       <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3936,7 +3983,7 @@
         <v>43125000</v>
       </c>
       <c r="N16" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -4020,67 +4067,67 @@
         <v>138750000</v>
       </c>
       <c r="AP16" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ16" t="n">
+        <v>73994324.61904761</v>
+      </c>
+      <c r="AR16" t="n">
         <v>20333333.33333333</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
       <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA16" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB16" t="n">
         <v>205263157.8947369</v>
       </c>
-      <c r="BB16" t="n">
-        <v>582207731.7186772</v>
-      </c>
       <c r="BC16" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD16" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BE16" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
       <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG16" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH16" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI16" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1877348.375</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -4113,6 +4160,9 @@
         <v>0</v>
       </c>
       <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4157,7 +4207,7 @@
         <v>43125000</v>
       </c>
       <c r="N17" t="n">
-        <v>65982951.5223497</v>
+        <v>65982951.52173913</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -4241,74 +4291,74 @@
         <v>126250000</v>
       </c>
       <c r="AP17" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
       </c>
       <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>437500000</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
       <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA17" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB17" t="n">
         <v>205263157.8947369</v>
       </c>
-      <c r="BB17" t="n">
-        <v>582207731.7186772</v>
-      </c>
       <c r="BC17" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD17" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
       <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG17" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH17" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI17" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ17" t="n">
+        <v>1877348.375</v>
+      </c>
+      <c r="BK17" t="n">
         <v>40000000</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BL17" t="n">
         <v>51250000</v>
       </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
       <c r="BM17" t="n">
         <v>0</v>
       </c>
@@ -4334,6 +4384,9 @@
         <v>0</v>
       </c>
       <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4462,80 +4515,80 @@
         <v>120000000</v>
       </c>
       <c r="AP18" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
       </c>
       <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>291666666.6666667</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>91000000</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>14875000</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>28750000</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>30000000</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
       <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA18" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB18" t="n">
         <v>205263157.8947369</v>
       </c>
-      <c r="BB18" t="n">
-        <v>582207731.7186772</v>
-      </c>
       <c r="BC18" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD18" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
       <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG18" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH18" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI18" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ18" t="n">
+        <v>1877348.375</v>
+      </c>
+      <c r="BK18" t="n">
         <v>60000000</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BL18" t="n">
         <v>153750000</v>
       </c>
-      <c r="BL18" t="n">
-        <v>362950058.0720093</v>
-      </c>
       <c r="BM18" t="n">
+        <v>327778579</v>
+      </c>
+      <c r="BN18" t="n">
         <v>33333333.33333333</v>
       </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
@@ -4555,6 +4608,9 @@
         <v>0</v>
       </c>
       <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4683,7 +4739,7 @@
         <v>120000000</v>
       </c>
       <c r="AP19" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4698,84 +4754,87 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>9583333.333333334</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>20000000</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>13636363.63636364</v>
       </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
       <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>96750000</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA19" t="n">
+        <v>121322414.375</v>
+      </c>
+      <c r="BB19" t="n">
         <v>136842105.2631579</v>
       </c>
-      <c r="BB19" t="n">
-        <v>582207731.7186772</v>
-      </c>
       <c r="BC19" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD19" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BE19" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
       <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG19" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH19" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI19" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1877348.375</v>
       </c>
       <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
         <v>153750000</v>
       </c>
-      <c r="BL19" t="n">
-        <v>362950058.0720093</v>
-      </c>
       <c r="BM19" t="n">
+        <v>327778579</v>
+      </c>
+      <c r="BN19" t="n">
         <v>100000000</v>
       </c>
-      <c r="BN19" t="n">
-        <v>0</v>
-      </c>
       <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
         <v>100000000</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BQ19" t="n">
         <v>7000000</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BR19" t="n">
         <v>608333333.3333334</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="BS19" t="n">
         <v>44964000</v>
       </c>
-      <c r="BS19" t="n">
-        <v>0</v>
-      </c>
       <c r="BT19" t="n">
         <v>0</v>
       </c>
       <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4904,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>117647058.8235294</v>
+        <v>23529411.76470588</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -4931,72 +4990,75 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>32250000</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>121322414.3160449</v>
-      </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>121322414.375</v>
       </c>
       <c r="BB20" t="n">
-        <v>582207731.7186772</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD20" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
       <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG20" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH20" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI20" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1877348.375</v>
       </c>
       <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
         <v>153750000</v>
       </c>
-      <c r="BL20" t="n">
-        <v>362950058.0720093</v>
-      </c>
       <c r="BM20" t="n">
+        <v>327778579</v>
+      </c>
+      <c r="BN20" t="n">
         <v>100000000</v>
       </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
       <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
         <v>100000000</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BQ20" t="n">
         <v>7000000</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BR20" t="n">
         <v>912500000</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="BS20" t="n">
         <v>120000000</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="BT20" t="n">
         <v>1337500</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="BU20" t="n">
         <v>916666.6666666666</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="BV20" t="n">
         <v>33333333.33333333</v>
       </c>
     </row>
@@ -5161,63 +5223,66 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>582207731.7186772</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
+        <v>582207731.75</v>
+      </c>
+      <c r="BD21" t="n">
         <v>15000000</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
         <v>25000000</v>
       </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
       <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
         <v>125000000</v>
       </c>
-      <c r="BG21" t="n">
-        <v>127966496.044672</v>
-      </c>
       <c r="BH21" t="n">
-        <v>28966961.37738483</v>
+        <v>127966496</v>
       </c>
       <c r="BI21" t="n">
-        <v>1877348.40029762</v>
+        <v>28966961.375</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1877348.375</v>
       </c>
       <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
         <v>153750000</v>
       </c>
-      <c r="BL21" t="n">
-        <v>362950058.0720093</v>
-      </c>
       <c r="BM21" t="n">
+        <v>327778579</v>
+      </c>
+      <c r="BN21" t="n">
         <v>100000000</v>
       </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
       <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
         <v>100000000</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BQ21" t="n">
         <v>7000000</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BR21" t="n">
         <v>912500000</v>
       </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
       <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
         <v>1337500</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="BU21" t="n">
         <v>2750000</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="BV21" t="n">
         <v>100000000</v>
       </c>
     </row>
